--- a/SubRES_TMPL/SubRES_SRV_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_SRV_NewTechs_Trans.xlsx
@@ -512,7 +512,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="274">
   <si>
     <t>LimType</t>
   </si>
@@ -1129,232 +1129,229 @@
     <t>~TFM_Fill-R: w=BY_S-SC; Hcol=Region</t>
   </si>
   <si>
+    <t>S-SH-CS_ELC-HP_X0</t>
+  </si>
+  <si>
+    <t>S-SH-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-SH-CS_GAS_X0</t>
+  </si>
+  <si>
+    <t>S-SH-CS_LPG_X0</t>
+  </si>
+  <si>
+    <t>S-SH-CS_OIL_X0</t>
+  </si>
+  <si>
+    <t>S-SH-CS_SOL_X0</t>
+  </si>
+  <si>
+    <t>S-SH-PU_BIO_X0</t>
+  </si>
+  <si>
+    <t>S-SH-PU_COA_X0</t>
+  </si>
+  <si>
+    <t>S-SH-PU_ELC-HP_X0</t>
+  </si>
+  <si>
+    <t>S-SH-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-SH-PU_GAS_X0</t>
+  </si>
+  <si>
     <t>S-SH-PU_LPG_X0</t>
   </si>
   <si>
-    <t>S-SH-PU_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-SH-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-SH-PU_ELC-HP_X0</t>
-  </si>
-  <si>
-    <t>S-SH-PU_COA_X0</t>
-  </si>
-  <si>
-    <t>S-SH-PU_BIO_X0</t>
-  </si>
-  <si>
-    <t>S-SH-CS_SOL_X0</t>
-  </si>
-  <si>
-    <t>S-SH-CS_OIL_X0</t>
-  </si>
-  <si>
-    <t>S-SH-CS_LPG_X0</t>
-  </si>
-  <si>
-    <t>S-SH-CS_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-SH-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-SH-CS_ELC-HP_X0</t>
+    <t>S-SH-PU_OIL_X0</t>
+  </si>
+  <si>
+    <t>S-SH-PU_SOL_X0</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>ANNUAL</t>
+  </si>
+  <si>
+    <t>S-WH-CS_BIO_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_COA_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_GAS_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_LPG_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_OIL_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_SOL_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_BIO_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_COA_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_GAS_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_LPG_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_OIL_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_SOL_X0</t>
+  </si>
+  <si>
+    <t>S-SC-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-SC-CS_GAS_X0</t>
+  </si>
+  <si>
+    <t>S-SC-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-SC-PU_GAS_X0</t>
+  </si>
+  <si>
+    <t>SRVWH-PU</t>
+  </si>
+  <si>
+    <t>SRVWH-CS</t>
+  </si>
+  <si>
+    <t>SRVSC-PU</t>
+  </si>
+  <si>
+    <t>SRVSC-CS</t>
+  </si>
+  <si>
+    <t>~TFM_UPD</t>
+  </si>
+  <si>
+    <t>AFA for SRV techs</t>
+  </si>
+  <si>
+    <t>EFF for SRV techs</t>
+  </si>
+  <si>
+    <t>CEFF</t>
+  </si>
+  <si>
+    <t>~TFM_Fill-R: w=BY_S-EAP; Hcol=Region</t>
+  </si>
+  <si>
+    <t>S-LIG*, S-REF*, S-OEL*, S-PLIG*</t>
+  </si>
+  <si>
+    <t>S-REF-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-REF-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-PLIG-PU_X3</t>
+  </si>
+  <si>
+    <t>S-PLIG-PU_X4</t>
+  </si>
+  <si>
+    <t>S-OEL-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-OEL-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-LIG-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-LIG-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-PLIG-PU_X1</t>
+  </si>
+  <si>
+    <t>S-PLIG-PU_X2</t>
+  </si>
+  <si>
+    <t>*Electric appliances</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>S-PLIG*</t>
+  </si>
+  <si>
+    <t>EFF*Stock</t>
+  </si>
+  <si>
+    <t>TIMES-Ireland Model</t>
+  </si>
+  <si>
+    <t>Sector(s):</t>
+  </si>
+  <si>
+    <t>Purpose:</t>
+  </si>
+  <si>
+    <t>Original developer(s):</t>
+  </si>
+  <si>
+    <t>Current maintainer(s):</t>
+  </si>
+  <si>
+    <t>Part of TIM version:</t>
+  </si>
+  <si>
+    <t>Model repository:</t>
+  </si>
+  <si>
+    <t>https://github.com/MaREI-EPMG/TIMES-Ireland-model</t>
+  </si>
+  <si>
+    <t>Licence:</t>
+  </si>
+  <si>
+    <t>CC BY-NC-SA 4.0 (unless specified otherwise)</t>
+  </si>
+  <si>
+    <t>https://creativecommons.org/licenses/by-nc-sa/4.0/</t>
+  </si>
+  <si>
+    <t>New Technologies - Transformation</t>
+  </si>
+  <si>
+    <t>Service sector (SRV)</t>
+  </si>
+  <si>
+    <t>Transform techno-economic data</t>
+  </si>
+  <si>
+    <t>Olexandr Balyk (UCC, olexandr.balyk@ucc.ie)</t>
   </si>
   <si>
     <t>S-SH-CS_COA_X0</t>
   </si>
   <si>
     <t>S-SH-CS_BIO_X0</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>year2</t>
-  </si>
-  <si>
-    <t>ANNUAL</t>
-  </si>
-  <si>
-    <t>S-WH-PU_SOL_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_OIL_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_LPG_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_COA_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_BIO_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_SOL_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_OIL_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_LPG_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_COA_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_BIO_X0</t>
-  </si>
-  <si>
-    <t>S-SC-PU_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-SC-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-SC-CS_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-SC-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>SRVWH-PU</t>
-  </si>
-  <si>
-    <t>SRVWH-CS</t>
-  </si>
-  <si>
-    <t>SRVSC-PU</t>
-  </si>
-  <si>
-    <t>SRVSC-CS</t>
-  </si>
-  <si>
-    <t>~TFM_UPD</t>
-  </si>
-  <si>
-    <t>AFA for SRV techs</t>
-  </si>
-  <si>
-    <t>EFF for SRV techs</t>
-  </si>
-  <si>
-    <t>CEFF</t>
-  </si>
-  <si>
-    <t>~TFM_Fill-R: w=BY_S-EAP; Hcol=Region</t>
-  </si>
-  <si>
-    <t>S-LIG*, S-REF*, S-OEL*, S-PLIG*</t>
-  </si>
-  <si>
-    <t>S-LIG-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-LIG-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-OEL-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-OEL-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-PLIG-PU_X2</t>
-  </si>
-  <si>
-    <t>S-PLIG-PU_X1</t>
-  </si>
-  <si>
-    <t>S-PLIG-PU_X4</t>
-  </si>
-  <si>
-    <t>S-PLIG-PU_X3</t>
-  </si>
-  <si>
-    <t>S-REF-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-REF-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>*Electric appliances</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>S-PLIG*</t>
-  </si>
-  <si>
-    <t>EFF*Stock</t>
-  </si>
-  <si>
-    <t>TIMES-Ireland Model</t>
-  </si>
-  <si>
-    <t>Sector(s):</t>
-  </si>
-  <si>
-    <t>Purpose:</t>
-  </si>
-  <si>
-    <t>Original developer(s):</t>
-  </si>
-  <si>
-    <t>Current maintainer(s):</t>
-  </si>
-  <si>
-    <t>Part of TIM version:</t>
-  </si>
-  <si>
-    <t>Model repository:</t>
-  </si>
-  <si>
-    <t>https://github.com/MaREI-EPMG/TIMES-Ireland-model</t>
-  </si>
-  <si>
-    <t>Licence:</t>
-  </si>
-  <si>
-    <t>CC BY-NC-SA 4.0 (unless specified otherwise)</t>
-  </si>
-  <si>
-    <t>https://creativecommons.org/licenses/by-nc-sa/4.0/</t>
-  </si>
-  <si>
-    <t>New Technologies - Transformation</t>
-  </si>
-  <si>
-    <t>Service sector (SRV)</t>
-  </si>
-  <si>
-    <t>Transform techno-economic data</t>
-  </si>
-  <si>
-    <t>Olexandr Balyk (UCC, olexandr.balyk@ucc.ie)</t>
-  </si>
-  <si>
-    <t>S-SH-PU_OIL_X0</t>
-  </si>
-  <si>
-    <t>S-SH-PU_SOL_X0</t>
   </si>
 </sst>
 </file>
@@ -1517,14 +1514,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="7" tint="-0.499430000782013"/>
+      <color theme="7" tint="-0.499419987201691"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="7" tint="-0.499430000782013"/>
+      <color theme="7" tint="-0.499419987201691"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1559,7 +1556,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0494400002062321"/>
+        <fgColor theme="0" tint="-0.049430001527071"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1613,7 +1610,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1494500041008"/>
+        <fgColor theme="0" tint="-0.149440005421638"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2261,7 +2258,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect l="4536" t="8851" r="7664" b="12843"/>
+        <a:srcRect l="4534" t="8850" r="7662" b="12841"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2388,7 +2385,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId5"/>
-        <a:srcRect l="1286" t="6481" r="3929" b="6254"/>
+        <a:srcRect l="1284" t="6480" r="3927" b="6253"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2431,7 +2428,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId6"/>
-        <a:srcRect l="3916" t="26116" r="3916" b="26115"/>
+        <a:srcRect l="3915" t="26115" r="3915" b="26113"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3378,7 +3375,7 @@
     </row>
     <row r="16" spans="1:26" ht="102.75" customHeight="1">
       <c r="A16" s="75" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B16" s="75"/>
       <c r="C16" s="75"/>
@@ -3467,7 +3464,7 @@
         <v>31</v>
       </c>
       <c r="B19" s="74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C19" s="74"/>
       <c r="D19" s="74"/>
@@ -3496,10 +3493,10 @@
     </row>
     <row r="20" spans="1:26" ht="17.25" customHeight="1">
       <c r="A20" s="66" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B20" s="74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C20" s="74"/>
       <c r="D20" s="74"/>
@@ -3528,10 +3525,10 @@
     </row>
     <row r="21" spans="1:26" ht="17.25" customHeight="1">
       <c r="A21" s="66" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B21" s="69" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C21" s="69"/>
       <c r="D21" s="69"/>
@@ -3588,7 +3585,7 @@
     </row>
     <row r="23" spans="1:26" ht="17.25" customHeight="1">
       <c r="A23" s="66" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
@@ -3674,10 +3671,10 @@
     </row>
     <row r="26" spans="1:26" ht="17.25" customHeight="1">
       <c r="A26" s="66" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B26" s="74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C26" s="74"/>
       <c r="D26" s="74"/>
@@ -3762,7 +3759,7 @@
     </row>
     <row r="29" spans="1:26" ht="17.25" customHeight="1">
       <c r="A29" s="66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B29" s="70">
         <v>1</v>
@@ -3794,10 +3791,10 @@
     </row>
     <row r="30" spans="1:26" ht="17.25" customHeight="1">
       <c r="A30" s="66" t="s">
+        <v>263</v>
+      </c>
+      <c r="B30" s="76" t="s">
         <v>264</v>
-      </c>
-      <c r="B30" s="76" t="s">
-        <v>265</v>
       </c>
       <c r="C30" s="74"/>
       <c r="D30" s="74"/>
@@ -3826,10 +3823,10 @@
     </row>
     <row r="31" spans="1:26" ht="17.25" customHeight="1">
       <c r="A31" s="66" t="s">
+        <v>265</v>
+      </c>
+      <c r="B31" s="74" t="s">
         <v>266</v>
-      </c>
-      <c r="B31" s="74" t="s">
-        <v>267</v>
       </c>
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
@@ -3859,7 +3856,7 @@
     <row r="32" spans="1:26" ht="17.25" customHeight="1">
       <c r="A32" s="72"/>
       <c r="B32" s="73" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C32" s="72"/>
       <c r="D32" s="72"/>
@@ -5831,9 +5828,6 @@
       <c r="M1" t="s">
         <v>130</v>
       </c>
-      <c r="N1" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="15">
       <c r="A2" t="s">
@@ -5843,7 +5837,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -5874,9 +5868,6 @@
       </c>
       <c r="M2">
         <v>0.0342465753424658</v>
-      </c>
-      <c r="N2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15">
@@ -5887,7 +5878,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -5918,9 +5909,6 @@
       </c>
       <c r="M3">
         <v>0.0342465753424658</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -5963,9 +5951,6 @@
       <c r="M4">
         <v>0.0342465753424658</v>
       </c>
-      <c r="N4" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="5" spans="1:14" ht="15">
       <c r="A5" t="s">
@@ -5975,7 +5960,7 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -6006,9 +5991,6 @@
       </c>
       <c r="M5">
         <v>0.0342465753424658</v>
-      </c>
-      <c r="N5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15">
@@ -6019,7 +6001,7 @@
         <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -6028,7 +6010,7 @@
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G6" t="s">
         <v>213</v>
@@ -6050,9 +6032,6 @@
       </c>
       <c r="M6">
         <v>2.7466471585410202</v>
-      </c>
-      <c r="N6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
@@ -6063,7 +6042,7 @@
         <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -6072,7 +6051,7 @@
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G7" t="s">
         <v>213</v>
@@ -6094,9 +6073,6 @@
       </c>
       <c r="M7">
         <v>2.7679848891515602</v>
-      </c>
-      <c r="N7" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -6116,7 +6092,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G8" t="s">
         <v>213</v>
@@ -6138,9 +6114,6 @@
       </c>
       <c r="M8">
         <v>2.7466471585410202</v>
-      </c>
-      <c r="N8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -6151,7 +6124,7 @@
         <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -6160,7 +6133,7 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G9" t="s">
         <v>213</v>
@@ -6182,9 +6155,6 @@
       </c>
       <c r="M9">
         <v>2.7679848891515602</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -6242,9 +6212,6 @@
       <c r="M1" t="s">
         <v>130</v>
       </c>
-      <c r="N1" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="15">
       <c r="A2" t="s">
@@ -6254,7 +6221,7 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -6263,7 +6230,7 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G2" t="s">
         <v>213</v>
@@ -6285,9 +6252,6 @@
       </c>
       <c r="M2">
         <v>2.4973571887487398</v>
-      </c>
-      <c r="N2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15">
@@ -6298,7 +6262,7 @@
         <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -6307,7 +6271,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G3" t="s">
         <v>213</v>
@@ -6329,9 +6293,6 @@
       </c>
       <c r="M3">
         <v>4.3260777448279004</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -6351,7 +6312,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G4" t="s">
         <v>213</v>
@@ -6373,9 +6334,6 @@
       </c>
       <c r="M4">
         <v>1</v>
-      </c>
-      <c r="N4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15">
@@ -6386,7 +6344,7 @@
         <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -6395,7 +6353,7 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G5" t="s">
         <v>213</v>
@@ -6417,9 +6375,6 @@
       </c>
       <c r="M5">
         <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15">
@@ -6430,7 +6385,7 @@
         <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -6439,7 +6394,7 @@
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G6" t="s">
         <v>213</v>
@@ -6461,9 +6416,6 @@
       </c>
       <c r="M6">
         <v>0.48784295359637803</v>
-      </c>
-      <c r="N6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
@@ -6474,7 +6426,7 @@
         <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -6483,7 +6435,7 @@
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G7" t="s">
         <v>213</v>
@@ -6505,9 +6457,6 @@
       </c>
       <c r="M7">
         <v>0.37305637627958299</v>
-      </c>
-      <c r="N7" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -6518,7 +6467,7 @@
         <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -6527,7 +6476,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G8" t="s">
         <v>213</v>
@@ -6549,9 +6498,6 @@
       </c>
       <c r="M8">
         <v>0.31709791983764601</v>
-      </c>
-      <c r="N8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -6562,7 +6508,7 @@
         <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -6571,7 +6517,7 @@
         <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G9" t="s">
         <v>213</v>
@@ -6593,9 +6539,6 @@
       </c>
       <c r="M9">
         <v>1.2683916793505801</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15">
@@ -6606,7 +6549,7 @@
         <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6615,7 +6558,7 @@
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G10" t="s">
         <v>213</v>
@@ -6637,9 +6580,6 @@
       </c>
       <c r="M10">
         <v>33.491553664929803</v>
-      </c>
-      <c r="N10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15">
@@ -6650,7 +6590,7 @@
         <v>127</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -6659,7 +6599,7 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G11" t="s">
         <v>213</v>
@@ -6681,9 +6621,6 @@
       </c>
       <c r="M11">
         <v>58.016156280053501</v>
-      </c>
-      <c r="N11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15">
@@ -6691,10 +6628,10 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -6725,9 +6662,6 @@
       </c>
       <c r="M12">
         <v>0.019199999999999998</v>
-      </c>
-      <c r="N12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15">
@@ -6735,10 +6669,10 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -6769,9 +6703,6 @@
       </c>
       <c r="M13">
         <v>0.071999999999999995</v>
-      </c>
-      <c r="N13" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15">
@@ -6779,10 +6710,10 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -6813,9 +6744,6 @@
       </c>
       <c r="M14">
         <v>0.38400000000000001</v>
-      </c>
-      <c r="N14" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15">
@@ -6823,10 +6751,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -6857,9 +6785,6 @@
       </c>
       <c r="M15">
         <v>0.0047999999999999996</v>
-      </c>
-      <c r="N15" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7295,7 +7220,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23.25">
       <c r="A1" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15">
@@ -8168,7 +8093,7 @@
         <v>S-SH-PU_COA*</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D37" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H37,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8196,7 +8121,7 @@
         <v>S-SH-PU_LPG*</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D38" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H38,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8224,7 +8149,7 @@
         <v>S-SH-PU_OIL*</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D39" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H39,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8252,7 +8177,7 @@
         <v>S-SH-PU_GAS*</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D40" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H40,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8280,7 +8205,7 @@
         <v>S-SH-PU_BIO*</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D41" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H41,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8308,7 +8233,7 @@
         <v>S-SH-PU_ELC*</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D42" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H42,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8336,7 +8261,7 @@
         <v>S-SH-PU_HET*</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D43" s="8">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H43,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8364,7 +8289,7 @@
         <v>S-SH-CS_COA*</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D44" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H44,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8392,7 +8317,7 @@
         <v>S-SH-CS_LPG*</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D45" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H45,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8420,7 +8345,7 @@
         <v>S-SH-CS_OIL*</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D46" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H46,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8448,7 +8373,7 @@
         <v>S-SH-CS_GAS*</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D47" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H47,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8476,7 +8401,7 @@
         <v>S-SH-CS_BIO*</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D48" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H48,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8504,7 +8429,7 @@
         <v>S-SH-CS_ELC*</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D49" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H49,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8532,7 +8457,7 @@
         <v>S-SH-CS_HET*</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D50" s="13">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H50,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8631,7 +8556,7 @@
         <v>S-SH-PU_ELC*</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D55" s="7">
         <f>SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,AFA!H55,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"AFA")</f>
@@ -8658,7 +8583,7 @@
         <v>S-SH-CS_ELC*</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D56" s="13">
         <f>SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,AFA!H56,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"AFA")</f>
@@ -8702,12 +8627,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23.25">
       <c r="A1" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15">
       <c r="A2" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1">
@@ -8774,7 +8699,7 @@
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8802,7 +8727,7 @@
     </row>
     <row r="7" spans="1:8" ht="15">
       <c r="A7" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8830,7 +8755,7 @@
     </row>
     <row r="8" spans="1:8" ht="15">
       <c r="A8" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B8" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8858,7 +8783,7 @@
     </row>
     <row r="9" spans="1:8" ht="15">
       <c r="A9" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B9" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8886,7 +8811,7 @@
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>"S-SH-"&amp;F10&amp;"_"&amp;G10&amp;"*, -*N1"</f>
@@ -8914,7 +8839,7 @@
     </row>
     <row r="11" spans="1:8" ht="15">
       <c r="A11" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>"S-SH-"&amp;F11&amp;"_"&amp;G11&amp;"*N1"</f>
@@ -8942,7 +8867,7 @@
     </row>
     <row r="12" spans="1:8" ht="15">
       <c r="A12" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B12" s="4" t="str">
         <f t="shared" si="2" ref="B12:B13">"S-SH-"&amp;F12&amp;"_"&amp;G12&amp;"*"</f>
@@ -8998,7 +8923,7 @@
     </row>
     <row r="14" spans="1:8" ht="15">
       <c r="A14" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B14" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9026,7 +8951,7 @@
     </row>
     <row r="15" spans="1:8" ht="15">
       <c r="A15" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B15" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9054,7 +8979,7 @@
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9082,7 +9007,7 @@
     </row>
     <row r="17" spans="1:8" ht="15">
       <c r="A17" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B17" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9110,7 +9035,7 @@
     </row>
     <row r="18" spans="1:8" ht="15">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>"S-SH-"&amp;F18&amp;"_"&amp;G18&amp;"*, -*N1"</f>
@@ -9138,7 +9063,7 @@
     </row>
     <row r="19" spans="1:8" ht="15">
       <c r="A19" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>"S-SH-"&amp;F19&amp;"_"&amp;G19&amp;"*N1"</f>
@@ -9166,7 +9091,7 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1">
       <c r="A20" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" s="12" t="str">
         <f t="shared" si="5" ref="B20">"S-SH-"&amp;F20&amp;"_"&amp;G20&amp;"*"</f>
@@ -9212,7 +9137,7 @@
         <v>S-WH-PU_COA*</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D22" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H22,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9233,14 +9158,14 @@
     </row>
     <row r="23" spans="1:8" ht="15">
       <c r="A23" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B23" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_LPG*</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D23" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H23,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9268,7 +9193,7 @@
         <v>S-WH-PU_OIL*</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D24" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H24,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9289,14 +9214,14 @@
     </row>
     <row r="25" spans="1:8" ht="15">
       <c r="A25" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B25" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_GAS*</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D25" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H25,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9317,14 +9242,14 @@
     </row>
     <row r="26" spans="1:8" ht="15">
       <c r="A26" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B26" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_BIO*</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D26" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H26,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9345,14 +9270,14 @@
     </row>
     <row r="27" spans="1:8" ht="15">
       <c r="A27" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B27" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_SOL*</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D27" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H27,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9373,14 +9298,14 @@
     </row>
     <row r="28" spans="1:8" ht="15">
       <c r="A28" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B28" s="4" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_ELC*</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D28" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H28,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9408,7 +9333,7 @@
         <v>S-WH-CS_COA*</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D29" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H29,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9429,14 +9354,14 @@
     </row>
     <row r="30" spans="1:8" ht="15">
       <c r="A30" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B30" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_LPG*</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D30" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H30,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9464,7 +9389,7 @@
         <v>S-WH-CS_OIL*</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D31" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H31,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9485,14 +9410,14 @@
     </row>
     <row r="32" spans="1:8" ht="15">
       <c r="A32" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B32" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_GAS*</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D32" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H32,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9513,14 +9438,14 @@
     </row>
     <row r="33" spans="1:8" ht="15">
       <c r="A33" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_BIO*</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D33" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H33,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9541,14 +9466,14 @@
     </row>
     <row r="34" spans="1:8" ht="15">
       <c r="A34" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B34" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_SOL*</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D34" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H34,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9569,14 +9494,14 @@
     </row>
     <row r="35" spans="1:8" ht="15">
       <c r="A35" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B35" s="4" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_ELC*</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D35" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H35,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9615,7 +9540,7 @@
         <v>S-SH-PU_COA*</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D37" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H37,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9636,14 +9561,14 @@
     </row>
     <row r="38" spans="1:8" ht="15">
       <c r="A38" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B38" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_LPG*</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D38" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H38,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9664,14 +9589,14 @@
     </row>
     <row r="39" spans="1:8" ht="15">
       <c r="A39" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B39" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_OIL*</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D39" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H39,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9692,14 +9617,14 @@
     </row>
     <row r="40" spans="1:8" ht="15">
       <c r="A40" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B40" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_GAS*</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D40" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H40,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9720,14 +9645,14 @@
     </row>
     <row r="41" spans="1:8" ht="15">
       <c r="A41" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B41" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_BIO*</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D41" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H41,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9748,14 +9673,14 @@
     </row>
     <row r="42" spans="1:8" ht="15">
       <c r="A42" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B42" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_ELC*</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D42" s="58" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H42,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9776,14 +9701,14 @@
     </row>
     <row r="43" spans="1:8" ht="15">
       <c r="A43" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B43" s="4" t="str">
         <f t="shared" si="11" ref="B43">"S-SH-"&amp;F43&amp;"_"&amp;G43&amp;"*"</f>
         <v>S-SH-PU_HET*</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D43" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H43,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9811,7 +9736,7 @@
         <v>S-SH-CS_COA*</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D44" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H44,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9832,14 +9757,14 @@
     </row>
     <row r="45" spans="1:8" ht="15">
       <c r="A45" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B45" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_LPG*</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D45" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H45,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9860,14 +9785,14 @@
     </row>
     <row r="46" spans="1:8" ht="15">
       <c r="A46" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B46" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_OIL*</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D46" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H46,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9888,14 +9813,14 @@
     </row>
     <row r="47" spans="1:8" ht="15">
       <c r="A47" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B47" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_GAS*</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D47" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H47,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9916,14 +9841,14 @@
     </row>
     <row r="48" spans="1:8" ht="15">
       <c r="A48" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B48" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_BIO*</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D48" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H48,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9944,14 +9869,14 @@
     </row>
     <row r="49" spans="1:8" ht="15">
       <c r="A49" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B49" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_ELC*</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D49" s="58" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H49,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9972,14 +9897,14 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1">
       <c r="A50" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B50" s="12" t="str">
         <f t="shared" si="13" ref="B50">"S-SH-"&amp;F50&amp;"_"&amp;G50&amp;"*"</f>
         <v>S-SH-CS_HET*</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D50" s="13" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H50,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -10011,14 +9936,14 @@
     </row>
     <row r="52" spans="1:8" ht="15">
       <c r="A52" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B52" s="1" t="str">
         <f>"S-SC-"&amp;F52&amp;"_"&amp;G52&amp;"*"</f>
         <v>S-SC-PU_ELC*</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D52" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,EFF!H52,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"EFF")</f>
@@ -10038,14 +9963,14 @@
     </row>
     <row r="53" spans="1:8" ht="15">
       <c r="A53" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B53" s="4" t="str">
         <f>"S-SC-"&amp;F53&amp;"_"&amp;G53&amp;"*"</f>
         <v>S-SC-CS_ELC*</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D53" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,EFF!H53,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"EFF")</f>
@@ -10076,14 +10001,14 @@
     </row>
     <row r="55" spans="1:8" ht="15">
       <c r="A55" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B55" s="1" t="str">
         <f t="shared" si="14" ref="B55:B56">"S-SH-"&amp;F55&amp;"_"&amp;G55&amp;"*"</f>
         <v>S-SH-PU_ELC*</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D55" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,EFF!H55,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"EFF")</f>
@@ -10103,14 +10028,14 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1">
       <c r="A56" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B56" s="12" t="str">
         <f t="shared" si="14"/>
         <v>S-SH-CS_ELC*</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D56" s="13" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,EFF!H56,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"EFF")</f>
@@ -10130,7 +10055,7 @@
     </row>
     <row r="57" spans="1:8" ht="15">
       <c r="A57" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
@@ -10267,7 +10192,7 @@
       <c r="K62" s="54"/>
       <c r="L62" s="54"/>
       <c r="M62" s="55" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="15">
@@ -10708,7 +10633,7 @@
     </row>
     <row r="18" spans="2:10" ht="15">
       <c r="B18" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -10764,7 +10689,7 @@
       </c>
       <c r="G20" s="20"/>
       <c r="H20" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
@@ -10775,7 +10700,7 @@
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E21" s="18">
         <v>2018</v>
@@ -10785,7 +10710,7 @@
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
@@ -11787,9 +11712,6 @@
       <c r="M1" t="s">
         <v>130</v>
       </c>
-      <c r="N1" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="15">
       <c r="A2" t="s">
@@ -11799,7 +11721,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -11830,9 +11752,6 @@
       </c>
       <c r="M2">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15">
@@ -11843,7 +11762,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -11874,9 +11793,6 @@
       </c>
       <c r="M3">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -11887,7 +11803,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -11918,9 +11834,6 @@
       </c>
       <c r="M4">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15">
@@ -11931,7 +11844,7 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -11962,9 +11875,6 @@
       </c>
       <c r="M5">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15">
@@ -11975,7 +11885,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -12006,9 +11916,6 @@
       </c>
       <c r="M6">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
@@ -12019,7 +11926,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -12050,9 +11957,6 @@
       </c>
       <c r="M7">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N7" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -12063,7 +11967,7 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -12094,9 +11998,6 @@
       </c>
       <c r="M8">
         <v>0.116438356164384</v>
-      </c>
-      <c r="N8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -12107,7 +12008,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -12138,9 +12039,6 @@
       </c>
       <c r="M9">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15">
@@ -12151,7 +12049,7 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -12182,9 +12080,6 @@
       </c>
       <c r="M10">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15">
@@ -12195,7 +12090,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -12226,9 +12121,6 @@
       </c>
       <c r="M11">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15">
@@ -12239,7 +12131,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -12270,9 +12162,6 @@
       </c>
       <c r="M12">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15">
@@ -12283,7 +12172,7 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -12314,9 +12203,6 @@
       </c>
       <c r="M13">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N13" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15">
@@ -12327,7 +12213,7 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -12358,9 +12244,6 @@
       </c>
       <c r="M14">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N14" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15">
@@ -12371,7 +12254,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -12402,9 +12285,6 @@
       </c>
       <c r="M15">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N15" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15">
@@ -12415,7 +12295,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -12446,9 +12326,6 @@
       </c>
       <c r="M16">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N16" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15">
@@ -12459,7 +12336,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -12490,9 +12367,6 @@
       </c>
       <c r="M17">
         <v>0.114155251141553</v>
-      </c>
-      <c r="N17" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15">
@@ -12503,7 +12377,7 @@
         <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -12512,7 +12386,7 @@
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G18" t="s">
         <v>213</v>
@@ -12534,9 +12408,6 @@
       </c>
       <c r="M18">
         <v>0.63490443337371305</v>
-      </c>
-      <c r="N18" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15">
@@ -12547,7 +12418,7 @@
         <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -12556,7 +12427,7 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G19" t="s">
         <v>213</v>
@@ -12578,9 +12449,6 @@
       </c>
       <c r="M19">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15">
@@ -12591,7 +12459,7 @@
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
@@ -12600,7 +12468,7 @@
         <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G20" t="s">
         <v>213</v>
@@ -12622,9 +12490,6 @@
       </c>
       <c r="M20">
         <v>2.1000000000000001</v>
-      </c>
-      <c r="N20" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15">
@@ -12635,7 +12500,7 @@
         <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D21" t="s">
         <v>17</v>
@@ -12644,7 +12509,7 @@
         <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G21" t="s">
         <v>213</v>
@@ -12666,9 +12531,6 @@
       </c>
       <c r="M21">
         <v>0.81595511259153497</v>
-      </c>
-      <c r="N21" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15">
@@ -12679,7 +12541,7 @@
         <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -12688,7 +12550,7 @@
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G22" t="s">
         <v>213</v>
@@ -12710,9 +12572,6 @@
       </c>
       <c r="M22">
         <v>0.77299617086321304</v>
-      </c>
-      <c r="N22" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15">
@@ -12723,7 +12582,7 @@
         <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -12732,7 +12591,7 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G23" t="s">
         <v>213</v>
@@ -12754,9 +12613,6 @@
       </c>
       <c r="M23">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N23" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15">
@@ -12767,7 +12623,7 @@
         <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -12776,7 +12632,7 @@
         <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G24" t="s">
         <v>213</v>
@@ -12798,9 +12654,6 @@
       </c>
       <c r="M24">
         <v>0.65835584489725196</v>
-      </c>
-      <c r="N24" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15">
@@ -12811,7 +12664,7 @@
         <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -12820,7 +12673,7 @@
         <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G25" t="s">
         <v>213</v>
@@ -12842,9 +12695,6 @@
       </c>
       <c r="M25">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N25" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15">
@@ -12855,7 +12705,7 @@
         <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -12864,7 +12714,7 @@
         <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G26" t="s">
         <v>213</v>
@@ -12886,9 +12736,6 @@
       </c>
       <c r="M26">
         <v>0.63490443337371305</v>
-      </c>
-      <c r="N26" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15">
@@ -12899,7 +12746,7 @@
         <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -12908,7 +12755,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G27" t="s">
         <v>213</v>
@@ -12930,9 +12777,6 @@
       </c>
       <c r="M27">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N27" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15">
@@ -12943,7 +12787,7 @@
         <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -12952,7 +12796,7 @@
         <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G28" t="s">
         <v>213</v>
@@ -12974,9 +12818,6 @@
       </c>
       <c r="M28">
         <v>2.1000000000000001</v>
-      </c>
-      <c r="N28" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15">
@@ -12987,7 +12828,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -12996,7 +12837,7 @@
         <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G29" t="s">
         <v>213</v>
@@ -13018,9 +12859,6 @@
       </c>
       <c r="M29">
         <v>0.81595511259153497</v>
-      </c>
-      <c r="N29" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15">
@@ -13031,7 +12869,7 @@
         <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -13040,7 +12878,7 @@
         <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G30" t="s">
         <v>213</v>
@@ -13062,9 +12900,6 @@
       </c>
       <c r="M30">
         <v>0.77299617086321304</v>
-      </c>
-      <c r="N30" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15">
@@ -13075,7 +12910,7 @@
         <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -13084,7 +12919,7 @@
         <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G31" t="s">
         <v>213</v>
@@ -13106,9 +12941,6 @@
       </c>
       <c r="M31">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N31" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15">
@@ -13119,7 +12951,7 @@
         <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -13128,7 +12960,7 @@
         <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G32" t="s">
         <v>213</v>
@@ -13150,9 +12982,6 @@
       </c>
       <c r="M32">
         <v>0.65835584489725196</v>
-      </c>
-      <c r="N32" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15">
@@ -13163,7 +12992,7 @@
         <v>127</v>
       </c>
       <c r="C33" t="s">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -13172,7 +13001,7 @@
         <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G33" t="s">
         <v>213</v>
@@ -13194,9 +13023,6 @@
       </c>
       <c r="M33">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N33" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -13254,9 +13080,6 @@
       <c r="M1" t="s">
         <v>130</v>
       </c>
-      <c r="N1" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="15">
       <c r="A2" t="s">
@@ -13266,7 +13089,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
@@ -13297,9 +13120,6 @@
       </c>
       <c r="M2">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15">
@@ -13310,7 +13130,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -13341,9 +13161,6 @@
       </c>
       <c r="M3">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -13354,7 +13171,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -13385,9 +13202,6 @@
       </c>
       <c r="M4">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15">
@@ -13398,7 +13212,7 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -13429,9 +13243,6 @@
       </c>
       <c r="M5">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15">
@@ -13442,7 +13253,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -13473,9 +13284,6 @@
       </c>
       <c r="M6">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N6" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
@@ -13486,7 +13294,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -13517,9 +13325,6 @@
       </c>
       <c r="M7">
         <v>0.0232876712328767</v>
-      </c>
-      <c r="N7" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -13530,7 +13335,7 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -13561,9 +13366,6 @@
       </c>
       <c r="M8">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -13606,9 +13408,6 @@
       <c r="M9">
         <v>0.022831050228310501</v>
       </c>
-      <c r="N9" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="10" spans="1:14" ht="15">
       <c r="A10" t="s">
@@ -13618,7 +13417,7 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -13649,9 +13448,6 @@
       </c>
       <c r="M10">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15">
@@ -13662,7 +13458,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -13693,9 +13489,6 @@
       </c>
       <c r="M11">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15">
@@ -13706,7 +13499,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -13737,9 +13530,6 @@
       </c>
       <c r="M12">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15">
@@ -13750,7 +13540,7 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -13781,9 +13571,6 @@
       </c>
       <c r="M13">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N13" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15">
@@ -13794,7 +13581,7 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -13825,9 +13612,6 @@
       </c>
       <c r="M14">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N14" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15">
@@ -13838,7 +13622,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -13869,9 +13653,6 @@
       </c>
       <c r="M15">
         <v>0.022831050228310501</v>
-      </c>
-      <c r="N15" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15">
@@ -13882,7 +13663,7 @@
         <v>127</v>
       </c>
       <c r="C16" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -13891,7 +13672,7 @@
         <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G16" t="s">
         <v>213</v>
@@ -13913,9 +13694,6 @@
       </c>
       <c r="M16">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N16" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15">
@@ -13926,7 +13704,7 @@
         <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -13935,7 +13713,7 @@
         <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G17" t="s">
         <v>213</v>
@@ -13957,9 +13735,6 @@
       </c>
       <c r="M17">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N17" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15">
@@ -13970,7 +13745,7 @@
         <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -13979,7 +13754,7 @@
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G18" t="s">
         <v>213</v>
@@ -14001,9 +13776,6 @@
       </c>
       <c r="M18">
         <v>0.77915338816094504</v>
-      </c>
-      <c r="N18" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15">
@@ -14014,7 +13786,7 @@
         <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -14023,7 +13795,7 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G19" t="s">
         <v>213</v>
@@ -14045,9 +13817,6 @@
       </c>
       <c r="M19">
         <v>0.63024757853709501</v>
-      </c>
-      <c r="N19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15">
@@ -14058,7 +13827,7 @@
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
@@ -14067,7 +13836,7 @@
         <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G20" t="s">
         <v>213</v>
@@ -14089,9 +13858,6 @@
       </c>
       <c r="M20">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N20" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15">
@@ -14102,7 +13868,7 @@
         <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D21" t="s">
         <v>17</v>
@@ -14111,7 +13877,7 @@
         <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G21" t="s">
         <v>213</v>
@@ -14133,9 +13899,6 @@
       </c>
       <c r="M21">
         <v>0.59834963673469899</v>
-      </c>
-      <c r="N21" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15">
@@ -14146,7 +13909,7 @@
         <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -14155,7 +13918,7 @@
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G22" t="s">
         <v>213</v>
@@ -14177,9 +13940,6 @@
       </c>
       <c r="M22">
         <v>1</v>
-      </c>
-      <c r="N22" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15">
@@ -14199,7 +13959,7 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G23" t="s">
         <v>213</v>
@@ -14221,9 +13981,6 @@
       </c>
       <c r="M23">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N23" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15">
@@ -14234,7 +13991,7 @@
         <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -14243,7 +14000,7 @@
         <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G24" t="s">
         <v>213</v>
@@ -14265,9 +14022,6 @@
       </c>
       <c r="M24">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N24" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15">
@@ -14278,7 +14032,7 @@
         <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -14287,7 +14041,7 @@
         <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G25" t="s">
         <v>213</v>
@@ -14309,9 +14063,6 @@
       </c>
       <c r="M25">
         <v>0.77915338816094504</v>
-      </c>
-      <c r="N25" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15">
@@ -14322,7 +14073,7 @@
         <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -14331,7 +14082,7 @@
         <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G26" t="s">
         <v>213</v>
@@ -14353,9 +14104,6 @@
       </c>
       <c r="M26">
         <v>0.63024757853709501</v>
-      </c>
-      <c r="N26" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15">
@@ -14366,7 +14114,7 @@
         <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -14375,7 +14123,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G27" t="s">
         <v>213</v>
@@ -14397,9 +14145,6 @@
       </c>
       <c r="M27">
         <v>0.33000000000000002</v>
-      </c>
-      <c r="N27" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15">
@@ -14410,7 +14155,7 @@
         <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -14419,7 +14164,7 @@
         <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G28" t="s">
         <v>213</v>
@@ -14441,9 +14186,6 @@
       </c>
       <c r="M28">
         <v>0.59834963673469899</v>
-      </c>
-      <c r="N28" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15">
@@ -14454,7 +14196,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -14463,7 +14205,7 @@
         <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G29" t="s">
         <v>213</v>
@@ -14485,9 +14227,6 @@
       </c>
       <c r="M29">
         <v>1</v>
-      </c>
-      <c r="N29" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
